--- a/data-manipulation-scripts/sheets-cleanup/sheets/FILTRO OLEO - 24_01.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/sheets/FILTRO OLEO - 24_01.xlsx
@@ -40,7 +40,7 @@
     <t>751320978769</t>
   </si>
   <si>
-    <t>FILTRO ÓLEO IRON FILTRO ARZER250 2014 176277</t>
+    <t>FILTRO ÓLEO IRON FAZER250 2014 176277</t>
   </si>
   <si>
     <t>7899248157224</t>
@@ -88,13 +88,13 @@
     <t>7899641837679</t>
   </si>
   <si>
-    <t>FILTRO OLEO VEDAMOTORS FILTRO AR ZER YS/ CROSSER150/ 2014</t>
+    <t>FILTRO OLEO VEDAMOTORS FAZER YS/ CROSSER150/ 2014</t>
   </si>
   <si>
     <t>7908073715827</t>
   </si>
   <si>
-    <t>FILTRO OLEO SMARTFILTRO OLEOX FILTRO AR ZER250/ LANDER250/ YZ/ WRF250</t>
+    <t>FILTRO OLEO SMARTFOX FAZER250/ LANDER250/ YZ/ WRF250</t>
   </si>
   <si>
     <t>7899248120297</t>
@@ -418,7 +418,9 @@
       <c r="C2" s="2">
         <v>9.0</v>
       </c>
-      <c r="D2" s="3"/>
+      <c r="D2" s="2">
+        <v>15.0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
@@ -430,7 +432,9 @@
       <c r="C3" s="2">
         <v>7.0</v>
       </c>
-      <c r="D3" s="3"/>
+      <c r="D3" s="2">
+        <v>20.0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
@@ -442,7 +446,9 @@
       <c r="C4" s="2">
         <v>4.0</v>
       </c>
-      <c r="D4" s="3"/>
+      <c r="D4" s="2">
+        <v>15.0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
@@ -454,7 +460,9 @@
       <c r="C5" s="2">
         <v>7.0</v>
       </c>
-      <c r="D5" s="3"/>
+      <c r="D5" s="2">
+        <v>15.0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
@@ -466,7 +474,9 @@
       <c r="C6" s="2">
         <v>7.0</v>
       </c>
-      <c r="D6" s="3"/>
+      <c r="D6" s="2">
+        <v>15.0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
@@ -478,7 +488,9 @@
       <c r="C7" s="2">
         <v>1.0</v>
       </c>
-      <c r="D7" s="3"/>
+      <c r="D7" s="2">
+        <v>15.0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
@@ -490,7 +502,9 @@
       <c r="C8" s="2">
         <v>2.0</v>
       </c>
-      <c r="D8" s="3"/>
+      <c r="D8" s="2">
+        <v>15.0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
@@ -502,7 +516,9 @@
       <c r="C9" s="2">
         <v>1.0</v>
       </c>
-      <c r="D9" s="3"/>
+      <c r="D9" s="2">
+        <v>15.0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
@@ -514,7 +530,9 @@
       <c r="C10" s="2">
         <v>1.0</v>
       </c>
-      <c r="D10" s="3"/>
+      <c r="D10" s="2">
+        <v>15.0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
@@ -526,7 +544,9 @@
       <c r="C11" s="2">
         <v>3.0</v>
       </c>
-      <c r="D11" s="3"/>
+      <c r="D11" s="2">
+        <v>15.0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
@@ -538,7 +558,9 @@
       <c r="C12" s="2">
         <v>7.0</v>
       </c>
-      <c r="D12" s="3"/>
+      <c r="D12" s="2">
+        <v>32.0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
@@ -550,7 +572,9 @@
       <c r="C13" s="2">
         <v>4.0</v>
       </c>
-      <c r="D13" s="3"/>
+      <c r="D13" s="2">
+        <v>30.0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
@@ -562,7 +586,9 @@
       <c r="C14" s="2">
         <v>2.0</v>
       </c>
-      <c r="D14" s="3"/>
+      <c r="D14" s="2">
+        <v>15.0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
@@ -574,7 +600,9 @@
       <c r="C15" s="2">
         <v>1.0</v>
       </c>
-      <c r="D15" s="3"/>
+      <c r="D15" s="2">
+        <v>15.0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
@@ -586,7 +614,9 @@
       <c r="C16" s="2">
         <v>1.0</v>
       </c>
-      <c r="D16" s="3"/>
+      <c r="D16" s="2">
+        <v>15.0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1"/>
